--- a/synoptic/data/Summary Cations_CLL_20240520.xlsx
+++ b/synoptic/data/Summary Cations_CLL_20240520.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\PR-wetlands\synoptic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D670BC84-4787-449A-84EA-F4025365A910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6E2387-E56E-4966-A734-4887CE2BCC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="112">
   <si>
     <t xml:space="preserve">No. </t>
   </si>
@@ -368,6 +368,9 @@
   <si>
     <t>low standard</t>
   </si>
+  <si>
+    <t>SAR</t>
+  </si>
 </sst>
 </file>
 
@@ -379,7 +382,7 @@
     <numFmt numFmtId="166" formatCode="dd/mmm/yyyy\ hh:mm"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -443,6 +446,12 @@
     <font>
       <sz val="8"/>
       <name val="MS Sans Serif"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -596,7 +605,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -767,6 +776,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5013,28 +5023,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>34</v>
       </c>
@@ -5054,7 +5064,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -5073,8 +5083,28 @@
       <c r="F7">
         <v>0.13520846148813609</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <f>B7/23</f>
+        <v>2.2343175085409845E-3</v>
+      </c>
+      <c r="J7">
+        <f>D7/39.1</f>
+        <v>1.1192762427150007E-3</v>
+      </c>
+      <c r="K7">
+        <f>E7/50</f>
+        <v>3.1275206970258619E-3</v>
+      </c>
+      <c r="L7">
+        <f>F7/24</f>
+        <v>5.6336858953390037E-3</v>
+      </c>
+      <c r="N7">
+        <f>H7/SQRT(K7+L7)</f>
+        <v>2.3870577615815319E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -5093,8 +5123,50 @@
       <c r="F8">
         <v>0.5567415943870877</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <f t="shared" ref="H8:H18" si="0">B8/23</f>
+        <v>9.2104846572986891E-3</v>
+      </c>
+      <c r="J8">
+        <f t="shared" ref="J8:K18" si="1">D8/39.1</f>
+        <v>4.5975722863294839E-3</v>
+      </c>
+      <c r="K8">
+        <f t="shared" ref="K8:K18" si="2">E8/50</f>
+        <v>1.2892519207868172E-2</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ref="L8:L18" si="3">F8/24</f>
+        <v>2.319756643279532E-2</v>
+      </c>
+      <c r="N8">
+        <f t="shared" ref="N8:N18" si="4">H8/SQRT(K8+L8)</f>
+        <v>4.8482893069312832E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N9" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -5113,8 +5185,28 @@
       <c r="F10">
         <v>97.277321361646941</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>7.5883674648096955</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="1"/>
+        <v>0.12326367675797859</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="2"/>
+        <v>0.26768201705678246</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="3"/>
+        <v>4.0532217234019559</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="4"/>
+        <v>3.6505731702758801</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -5133,8 +5225,28 @@
       <c r="F11">
         <v>45.287796160205687</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>10.513877235619375</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>0.21517869686407487</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>0.41614813468354117</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="3"/>
+        <v>1.886991506675237</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="4"/>
+        <v>6.927918444192338</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -5153,8 +5265,28 @@
       <c r="F12">
         <v>33.749696516072966</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>3.3007988325461657</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>8.3279303482432537E-2</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="2"/>
+        <v>0.14217164657857415</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>1.4062373548363736</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="4"/>
+        <v>2.6526271681574789</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -5173,8 +5305,28 @@
       <c r="F13">
         <v>92.18179268110471</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>7.465299806486863</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>0.11761896587832915</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="2"/>
+        <v>0.26234556311617541</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="3"/>
+        <v>3.8409080283793631</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="4"/>
+        <v>3.6853867876070692</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -5193,8 +5345,28 @@
       <c r="F14">
         <v>49.627111682100825</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>10.490977629853914</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>0.20069813613889043</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>0.39992437978074341</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="3"/>
+        <v>2.0677963200875342</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="4"/>
+        <v>6.6783312863923001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -5213,8 +5385,28 @@
       <c r="F15">
         <v>34.23073534123661</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>3.276307777270838</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>8.2378213637592859E-2</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>0.14211792093048009</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="3"/>
+        <v>1.4262806392181921</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="4"/>
+        <v>2.6161128576950081</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -5233,8 +5425,28 @@
       <c r="F16">
         <v>30.994175218097077</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>3.0918589868531776</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="1"/>
+        <v>7.676843510363196E-2</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="2"/>
+        <v>0.13309944285708342</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="3"/>
+        <v>1.2914239674207115</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="4"/>
+        <v>2.5905076735440939</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -5253,8 +5465,28 @@
       <c r="F17">
         <v>90.798673228338515</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>7.1877830397160283</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="1"/>
+        <v>0.11512586493305314</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="2"/>
+        <v>0.2543661266996462</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>3.7832780511807713</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="4"/>
+        <v>3.5770988185243304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -5273,8 +5505,28 @@
       <c r="F18">
         <v>45.885565462466701</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>10.494540194251368</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="1"/>
+        <v>0.20773152142221596</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="2"/>
+        <v>0.41776838904515523</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="3"/>
+        <v>1.9118985609361125</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="4"/>
+        <v>6.8756932972666585</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -5294,7 +5546,7 @@
         <v>36.621816438854999</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -5314,7 +5566,7 @@
         <v>29.999903028721363</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -5334,7 +5586,7 @@
         <v>35.519306665520979</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -5354,7 +5606,7 @@
         <v>33.271793858571726</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -5374,7 +5626,7 @@
         <v>35.168564137587921</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -5394,7 +5646,7 @@
         <v>54.573542023579769</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -5414,7 +5666,7 @@
         <v>31.294179248615656</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -5434,7 +5686,7 @@
         <v>27.334886844515296</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -5454,7 +5706,7 @@
         <v>35.079476114843466</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -5474,7 +5726,7 @@
         <v>28.764794088323779</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -5494,7 +5746,7 @@
         <v>33.712754264293466</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -5514,7 +5766,7 @@
         <v>32.162973375459593</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>70</v>
       </c>
@@ -5533,8 +5785,11 @@
       <c r="L33" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="T33" s="70" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>64</v>
       </c>
@@ -5561,19 +5816,39 @@
         <v>165.29449262183138</v>
       </c>
       <c r="J34">
-        <f t="shared" ref="I34:M34" si="0">D34*5</f>
+        <f t="shared" ref="J34:K34" si="5">D34*5</f>
         <v>4.7482424117880733</v>
       </c>
       <c r="K34">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>13.277484709298298</v>
       </c>
       <c r="L34">
         <f>F34*5</f>
         <v>95.849381845978428</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N34">
+        <f>H34/23</f>
+        <v>7.1867170705144074</v>
+      </c>
+      <c r="P34">
+        <f>J34/39.1</f>
+        <v>0.12143842485391491</v>
+      </c>
+      <c r="Q34">
+        <f>K34/24</f>
+        <v>0.55322852955409574</v>
+      </c>
+      <c r="R34">
+        <f>L34/40.78</f>
+        <v>2.3504017127508194</v>
+      </c>
+      <c r="T34" s="70">
+        <f>N34/SQRT(Q34+R34)</f>
+        <v>4.2175466226942131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -5596,23 +5871,43 @@
         <v>65</v>
       </c>
       <c r="H35">
-        <f t="shared" ref="H35:H39" si="1">B35*5</f>
+        <f t="shared" ref="H35:H39" si="6">B35*5</f>
         <v>221.47235209596198</v>
       </c>
       <c r="J35">
-        <f t="shared" ref="J35:J39" si="2">D35*5</f>
+        <f t="shared" ref="J35:J39" si="7">D35*5</f>
         <v>7.9825952269472165</v>
       </c>
       <c r="K35">
-        <f t="shared" ref="K35:K39" si="3">E35*5</f>
+        <f t="shared" ref="K35:K39" si="8">E35*5</f>
         <v>20.306964369737255</v>
       </c>
       <c r="L35">
-        <f t="shared" ref="L35:L39" si="4">F35*5</f>
+        <f t="shared" ref="L35:L39" si="9">F35*5</f>
         <v>43.898004279389355</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N35">
+        <f t="shared" ref="N35:N45" si="10">H35/23</f>
+        <v>9.6292326998244331</v>
+      </c>
+      <c r="P35">
+        <f t="shared" ref="P35:P45" si="11">J35/39.1</f>
+        <v>0.20415844570197483</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" ref="Q35:Q42" si="12">K35/24</f>
+        <v>0.84612351540571895</v>
+      </c>
+      <c r="R35">
+        <f t="shared" ref="R35:R45" si="13">L35/40.78</f>
+        <v>1.0764591534916468</v>
+      </c>
+      <c r="T35" s="70">
+        <f t="shared" ref="T35:T45" si="14">N35/SQRT(Q35+R35)</f>
+        <v>6.9446309332115481</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -5635,23 +5930,43 @@
         <v>66</v>
       </c>
       <c r="H36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>161.06607214496694</v>
       </c>
       <c r="J36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>4.2508221324235604</v>
       </c>
       <c r="K36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>12.964362142502932</v>
       </c>
       <c r="L36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>90.537903545445815</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N36">
+        <f t="shared" si="10"/>
+        <v>7.0028727019550843</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="11"/>
+        <v>0.10871667857860769</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="12"/>
+        <v>0.54018175593762219</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="13"/>
+        <v>2.2201545744346691</v>
+      </c>
+      <c r="T36" s="70">
+        <f t="shared" si="14"/>
+        <v>4.2149772131059207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -5674,23 +5989,43 @@
         <v>67</v>
       </c>
       <c r="H37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>221.69728699192856</v>
       </c>
       <c r="J37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>7.6468279889435919</v>
       </c>
       <c r="K37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>19.693462600967329</v>
       </c>
       <c r="L37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>48.784657365372979</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N37">
+        <f t="shared" si="10"/>
+        <v>9.6390124779099384</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="11"/>
+        <v>0.19557104831057778</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="12"/>
+        <v>0.82056094170697202</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="13"/>
+        <v>1.1962888024858505</v>
+      </c>
+      <c r="T37" s="70">
+        <f t="shared" si="14"/>
+        <v>6.7872800703383671</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>68</v>
       </c>
@@ -5713,23 +6048,43 @@
         <v>68</v>
       </c>
       <c r="H38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>156.25643962561966</v>
       </c>
       <c r="J38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>4.3352569205558913</v>
       </c>
       <c r="K38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>12.54892985247627</v>
       </c>
       <c r="L38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>88.727717513644222</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N38">
+        <f t="shared" si="10"/>
+        <v>6.7937582445921594</v>
+      </c>
+      <c r="P38">
+        <f t="shared" si="11"/>
+        <v>0.11087613607559824</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="12"/>
+        <v>0.5228720771865113</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="13"/>
+        <v>2.1757655103885294</v>
+      </c>
+      <c r="T38" s="70">
+        <f t="shared" si="14"/>
+        <v>4.1355931368937293</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>69</v>
       </c>
@@ -5752,23 +6107,43 @@
         <v>69</v>
       </c>
       <c r="H39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>224.27393919132334</v>
       </c>
       <c r="J39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="7"/>
         <v>7.9986349428862642</v>
       </c>
       <c r="K39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>20.688381939555267</v>
       </c>
       <c r="L39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>45.032290997868486</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N39">
+        <f t="shared" si="10"/>
+        <v>9.7510408344053623</v>
+      </c>
+      <c r="P39">
+        <f t="shared" si="11"/>
+        <v>0.20456866861601697</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="12"/>
+        <v>0.86201591414813616</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="13"/>
+        <v>1.1042739332483689</v>
+      </c>
+      <c r="T39" s="70">
+        <f t="shared" si="14"/>
+        <v>6.9538802360434842</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G40" t="s">
         <v>45</v>
       </c>
@@ -5787,8 +6162,28 @@
       <c r="L40">
         <v>33.749696516072966</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N40">
+        <f t="shared" si="10"/>
+        <v>3.3007988325461657</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="11"/>
+        <v>8.3279303482432537E-2</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="12"/>
+        <v>0.29619093037202943</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="13"/>
+        <v>0.82760413232155383</v>
+      </c>
+      <c r="T40" s="70">
+        <f t="shared" si="14"/>
+        <v>3.1136908981943789</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G41" t="s">
         <v>48</v>
       </c>
@@ -5807,8 +6202,28 @@
       <c r="L41">
         <v>34.23073534123661</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N41">
+        <f t="shared" si="10"/>
+        <v>3.276307777270838</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="11"/>
+        <v>8.2378213637592859E-2</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="12"/>
+        <v>0.29607900193850017</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="13"/>
+        <v>0.83940008193321747</v>
+      </c>
+      <c r="T41" s="70">
+        <f t="shared" si="14"/>
+        <v>3.0746460212234803</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G42" t="s">
         <v>49</v>
       </c>
@@ -5826,6 +6241,26 @@
       </c>
       <c r="L42">
         <v>30.994175218097077</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="10"/>
+        <v>3.0918589868531776</v>
+      </c>
+      <c r="P42">
+        <f t="shared" si="11"/>
+        <v>7.676843510363196E-2</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="12"/>
+        <v>0.27729050595225707</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="13"/>
+        <v>0.76003372285672088</v>
+      </c>
+      <c r="T42" s="70">
+        <f t="shared" si="14"/>
+        <v>3.035724932555492</v>
       </c>
     </row>
   </sheetData>
